--- a/www/download/IND.surplus_value.empe_hs.r.pc.rpO1.xlsx
+++ b/www/download/IND.surplus_value.empe_hs.r.pc.rpO1.xlsx
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Ochoa 1</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,7 +678,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -683,84 +688,84 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>225.76</t>
+          <t>2.25757901578717</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>216.57</t>
+          <t>2.16570226527192</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>208.54</t>
+          <t>2.08536798039144</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>207.02</t>
+          <t>2.07023426784449</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>216.87</t>
+          <t>2.16869427869003</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>210.91</t>
+          <t>2.10914134322984</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>203.3</t>
+          <t>2.0330029505631</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>210.78</t>
+          <t>2.10775848430947</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>222.03</t>
+          <t>2.22025630388242</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>208.79</t>
+          <t>2.08789475618108</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>207.89</t>
+          <t>2.07887907417676</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>201.68</t>
+          <t>2.01678653035757</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>194.79</t>
+          <t>1.9479108489885</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>187.31</t>
+          <t>1.87305440161396</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>181.33</t>
+          <t>1.81328006751808</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -770,84 +775,84 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>219.87</t>
+          <t>2.1987434316222</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>211.28</t>
+          <t>2.11280664285165</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>204.53</t>
+          <t>2.04531959289115</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>201.56</t>
+          <t>2.01559873788886</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>212.28</t>
+          <t>2.12278212505547</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>207.4</t>
+          <t>2.07400323501582</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>200.56</t>
+          <t>2.00558724431268</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>205.24</t>
+          <t>2.05238599378704</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>225.91</t>
+          <t>2.25912554669052</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>204.41</t>
+          <t>2.04412942726551</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>208.05</t>
+          <t>2.08052214122754</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>197.99</t>
+          <t>1.97989149024249</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>187.36</t>
+          <t>1.87363862157066</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>175</t>
+          <t>1.74998356712492</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>173.24</t>
+          <t>1.73237775197119</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -857,84 +862,84 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>212.89</t>
+          <t>2.12889189614144</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>205.62</t>
+          <t>2.05621028752067</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>199.41</t>
+          <t>1.99410147922406</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>198.83</t>
+          <t>1.98829544539092</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>207.87</t>
+          <t>2.07871014851119</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>205.12</t>
+          <t>2.05121729826648</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>199.32</t>
+          <t>1.99316667446273</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>205.6</t>
+          <t>2.05603614511928</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>235.47</t>
+          <t>2.35467643624466</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>201.28</t>
+          <t>2.01278086002286</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>202.59</t>
+          <t>2.02587343492773</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>194.21</t>
+          <t>1.94214967043566</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>189.83</t>
+          <t>1.89834550041023</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>193.55</t>
+          <t>1.93554599362718</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>188.6</t>
+          <t>1.88604919160307</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -944,84 +949,84 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>148.51</t>
+          <t>1.48513414295212</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>141.85</t>
+          <t>1.41847473817385</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>133.38</t>
+          <t>1.33379653085755</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>135.41</t>
+          <t>1.35410320823055</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>146.68</t>
+          <t>1.46679813804646</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>144.5</t>
+          <t>1.44498745103157</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>138.22</t>
+          <t>1.38224674708078</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>142.49</t>
+          <t>1.42494294037268</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>228.13</t>
+          <t>2.28129051500125</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>156.3</t>
+          <t>1.5629786580783</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>156.7</t>
+          <t>1.56699225312771</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>155.25</t>
+          <t>1.55253174322975</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>154.21</t>
+          <t>1.54207126990707</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>154.42</t>
+          <t>1.54418034145495</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>150.13</t>
+          <t>1.50131098122394</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1031,84 +1036,84 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>106.25</t>
+          <t>1.06248015327343</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>101.55</t>
+          <t>1.01545903352748</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>96.74</t>
+          <t>0.967445368778669</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>98.28</t>
+          <t>0.9827529203729</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>106.66</t>
+          <t>1.06658858840686</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>102.35</t>
+          <t>1.023499745318</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>97.81</t>
+          <t>0.978094657981355</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>101.93</t>
+          <t>1.01933583207463</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>110.07</t>
+          <t>1.10073199490121</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>106.03</t>
+          <t>1.0603160880001</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>110.63</t>
+          <t>1.10629975810837</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>114.02</t>
+          <t>1.14017930396556</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>116.13</t>
+          <t>1.16126228139957</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>116.76</t>
+          <t>1.16761821325767</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>117.68</t>
+          <t>1.17684793010923</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1118,84 +1123,84 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>294.25</t>
+          <t>2.94253442406748</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>265.82</t>
+          <t>2.6581520043331</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>247.04</t>
+          <t>2.47036936157194</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>243.91</t>
+          <t>2.4391023779</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>252.36</t>
+          <t>2.52364700279406</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>249.97</t>
+          <t>2.49971363191552</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>238.64</t>
+          <t>2.38637894919656</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>240.08</t>
+          <t>2.40077302067744</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>254.24</t>
+          <t>2.54244470216727</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>242.38</t>
+          <t>2.42377043405943</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>248.77</t>
+          <t>2.48772289878984</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>241.33</t>
+          <t>2.41332031848019</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>238.09</t>
+          <t>2.3809172721563</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>229.67</t>
+          <t>2.29672821099077</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>223.1</t>
+          <t>2.23097450364806</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1205,84 +1210,84 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>266.93</t>
+          <t>2.66932049681892</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>250.82</t>
+          <t>2.50820898563501</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>237.62</t>
+          <t>2.376210251147</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>231.87</t>
+          <t>2.31871102227124</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>238.44</t>
+          <t>2.38444163183155</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>228.19</t>
+          <t>2.28189269777214</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>216.27</t>
+          <t>2.16268741072223</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>217.83</t>
+          <t>2.17829352685953</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>224.08</t>
+          <t>2.2407713797456</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>210.9</t>
+          <t>2.1090244914224</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>210.3</t>
+          <t>2.1030355607352</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>202.03</t>
+          <t>2.02029225866366</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>191.89</t>
+          <t>1.91887894138025</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>186.33</t>
+          <t>1.86325482831785</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>180.45</t>
+          <t>1.80447538389898</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1292,84 +1297,84 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>257.59</t>
+          <t>2.57589525050955</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>249.13</t>
+          <t>2.49130245109944</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>240.54</t>
+          <t>2.40538065852176</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>240.51</t>
+          <t>2.40511312921354</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>254.91</t>
+          <t>2.54910209541684</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>249.19</t>
+          <t>2.49188147941359</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>239.11</t>
+          <t>2.39113066803107</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>246.84</t>
+          <t>2.46837172760578</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>275.86</t>
+          <t>2.75858867508923</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>247.39</t>
+          <t>2.47389501453645</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>247.73</t>
+          <t>2.47726236539441</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>245.81</t>
+          <t>2.45809659232384</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>241.07</t>
+          <t>2.41069060564864</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>242.84</t>
+          <t>2.42841272433425</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>235.42</t>
+          <t>2.35416667555386</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1379,84 +1384,84 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>183.46</t>
+          <t>1.83456076647395</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>175.93</t>
+          <t>1.7592898310721</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>168.3</t>
+          <t>1.68301006895205</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>166.52</t>
+          <t>1.66518717963314</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>178.31</t>
+          <t>1.7831015414047</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>172.07</t>
+          <t>1.72067803600199</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>163.93</t>
+          <t>1.63928617694901</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>169.79</t>
+          <t>1.69785351685562</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>211.94</t>
+          <t>2.1193781718256</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>172.21</t>
+          <t>1.72205405006229</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>176.22</t>
+          <t>1.76215935538221</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>171.37</t>
+          <t>1.71373184082995</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>165.24</t>
+          <t>1.65239984289418</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>167.05</t>
+          <t>1.67046330068013</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>165.5</t>
+          <t>1.6550410631994</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1466,84 +1471,84 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>213.54</t>
+          <t>2.13539828093552</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>202.98</t>
+          <t>2.02984609746032</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>194.77</t>
+          <t>1.94766018895637</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>196.62</t>
+          <t>1.9661588063342</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>211.03</t>
+          <t>2.11034167830958</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>202.2</t>
+          <t>2.02195086818658</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>195.03</t>
+          <t>1.95033679735139</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>195.7</t>
+          <t>1.95695296837311</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>205.67</t>
+          <t>2.05666964895683</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>202.5</t>
+          <t>2.02495477961977</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>201.24</t>
+          <t>2.01242234050907</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>186.9</t>
+          <t>1.86899049953022</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>178.91</t>
+          <t>1.78909929488055</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>172.24</t>
+          <t>1.72243471268231</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>171.34</t>
+          <t>1.7133754462836</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1553,84 +1558,84 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>274.75</t>
+          <t>2.74748130420999</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>266.12</t>
+          <t>2.66118834255519</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>259.46</t>
+          <t>2.59460674679434</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>256.76</t>
+          <t>2.56760131798025</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>269.24</t>
+          <t>2.69244780328076</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>261.62</t>
+          <t>2.61624663569088</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>251.15</t>
+          <t>2.51153641562404</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>259.52</t>
+          <t>2.59524907307165</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>270.69</t>
+          <t>2.70687723264279</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>259.79</t>
+          <t>2.59787614159389</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>265.87</t>
+          <t>2.65870223468244</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>257.82</t>
+          <t>2.57823254064404</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>245.38</t>
+          <t>2.45382137149806</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>239.91</t>
+          <t>2.39913641688565</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>232.79</t>
+          <t>2.32793086807244</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1640,84 +1645,84 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>240.21</t>
+          <t>2.40211555601019</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>234.32</t>
+          <t>2.34322287599719</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>226.16</t>
+          <t>2.26163037150522</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>227.57</t>
+          <t>2.27573371235046</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>239.74</t>
+          <t>2.39744096801898</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>236.27</t>
+          <t>2.36270051775683</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>228.22</t>
+          <t>2.28222452806918</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>232.49</t>
+          <t>2.32489421089709</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>269.41</t>
+          <t>2.69409244821643</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>239.73</t>
+          <t>2.39725191013476</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>246.53</t>
+          <t>2.46530219759496</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>242.93</t>
+          <t>2.4293489735593</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>238.24</t>
+          <t>2.38242101498152</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>232.38</t>
+          <t>2.32375983726313</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>226.27</t>
+          <t>2.26268246292079</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1727,84 +1732,84 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>232.11</t>
+          <t>2.32107137729561</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>223.35</t>
+          <t>2.23345569022115</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>211.94</t>
+          <t>2.11944377801326</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>208.16</t>
+          <t>2.08156972185217</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>218.82</t>
+          <t>2.18823017761019</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>213.32</t>
+          <t>2.13324020513742</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>207.16</t>
+          <t>2.07156354196402</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>215.5</t>
+          <t>2.15496247009834</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>244.49</t>
+          <t>2.44488305445042</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>223.7</t>
+          <t>2.23703235729449</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>229.16</t>
+          <t>2.29163133757842</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>223.19</t>
+          <t>2.23186472237457</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>235.73</t>
+          <t>2.35734173400734</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>237.79</t>
+          <t>2.37787267443179</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>231.32</t>
+          <t>2.31316808116113</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1814,84 +1819,84 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>286.76</t>
+          <t>2.8675979120389</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>275.84</t>
+          <t>2.75836163123783</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>266.15</t>
+          <t>2.66151654736132</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>259.05</t>
+          <t>2.59052020336579</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>263.61</t>
+          <t>2.63609292661345</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>254.26</t>
+          <t>2.54260259931966</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>248.37</t>
+          <t>2.48365128097707</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>252.79</t>
+          <t>2.52788793065018</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>278.05</t>
+          <t>2.78050117938112</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>249.8</t>
+          <t>2.49797285647994</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>250.34</t>
+          <t>2.50337825718435</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>243.23</t>
+          <t>2.43234395975073</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>232.6</t>
+          <t>2.32601852203402</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>223</t>
+          <t>2.22995401858683</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>219.04</t>
+          <t>2.19042850485076</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1901,84 +1906,84 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>213.89</t>
+          <t>2.13887912756863</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>205.14</t>
+          <t>2.05139475990129</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>210.66</t>
+          <t>2.10658105493921</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>210.81</t>
+          <t>2.10811717104517</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>223.34</t>
+          <t>2.23344292476534</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>218.61</t>
+          <t>2.18613324935992</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>211.2</t>
+          <t>2.11204866416857</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>221.71</t>
+          <t>2.217148384835</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>259.68</t>
+          <t>2.5967572194878</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>229.78</t>
+          <t>2.29781463430861</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>238.07</t>
+          <t>2.38071959428739</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>235.5</t>
+          <t>2.35496714392183</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>226.01</t>
+          <t>2.26007190170275</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>219.87</t>
+          <t>2.19868826421731</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>214.72</t>
+          <t>2.14719934995446</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1988,84 +1993,84 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>219.07</t>
+          <t>2.19074612757621</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>206.53</t>
+          <t>2.06532992583113</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>204.39</t>
+          <t>2.04387854763905</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>203.18</t>
+          <t>2.03178920076106</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>217.53</t>
+          <t>2.17525839173459</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>212.28</t>
+          <t>2.12276054683173</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>207.57</t>
+          <t>2.07566828117046</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>215.21</t>
+          <t>2.15208444270866</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>224.36</t>
+          <t>2.24362638615959</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>215.23</t>
+          <t>2.15234690541774</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>217.48</t>
+          <t>2.17482290742738</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>213.31</t>
+          <t>2.13305102197436</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>210.11</t>
+          <t>2.10110571434112</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>197.7</t>
+          <t>1.97695046159939</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>196.51</t>
+          <t>1.96506964250071</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Grécia</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2075,84 +2080,84 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>251.11</t>
+          <t>2.51105421465689</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>241.01</t>
+          <t>2.41009361538447</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>234.11</t>
+          <t>2.34114292558627</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>232.8</t>
+          <t>2.32798781805683</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>243.68</t>
+          <t>2.43676815659329</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>236.03</t>
+          <t>2.36030809253548</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>226.21</t>
+          <t>2.26212985304818</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>230.34</t>
+          <t>2.30336979759925</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>260.08</t>
+          <t>2.60079121906574</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>242.67</t>
+          <t>2.4267414451875</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>250.66</t>
+          <t>2.50655446560549</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>249.2</t>
+          <t>2.49197637109786</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>241.79</t>
+          <t>2.41786131506825</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>231.42</t>
+          <t>2.31415323636755</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>224.87</t>
+          <t>2.24872738933172</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2162,84 +2167,84 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>165.29</t>
+          <t>1.65287044685492</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>155.48</t>
+          <t>1.55476026712863</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>1.4799651880011</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>148.11</t>
+          <t>1.48108613999926</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>156.77</t>
+          <t>1.56765866610663</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>148.22</t>
+          <t>1.48220546522422</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>145.67</t>
+          <t>1.4567472556591</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>153.23</t>
+          <t>1.53229938974592</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>199.96</t>
+          <t>1.99963687384369</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>160.13</t>
+          <t>1.60126248061924</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>163.1</t>
+          <t>1.63095185516947</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>158.89</t>
+          <t>1.58891955247287</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>153.78</t>
+          <t>1.53776305733821</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>147.22</t>
+          <t>1.47219521845478</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>141.94</t>
+          <t>1.41940378669085</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2249,84 +2254,84 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>101.99</t>
+          <t>1.01990282437139</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>117.52</t>
+          <t>1.17516880961821</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>110.63</t>
+          <t>1.10629175158266</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>120.74</t>
+          <t>1.20741532477212</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>148.56</t>
+          <t>1.48560220274303</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>112.37</t>
+          <t>1.12370622368099</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>108.14</t>
+          <t>1.08135091620424</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>126.13</t>
+          <t>1.26134572399549</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>126.13</t>
+          <t>1.26133758090519</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>147.18</t>
+          <t>1.47183976114916</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>106.92</t>
+          <t>1.06916033281074</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>92.56</t>
+          <t>0.925601717963103</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>58.51</t>
+          <t>0.585144133124098</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>53.9</t>
+          <t>0.539004478574826</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>49.95</t>
+          <t>0.499467681221318</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Índia</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2336,84 +2341,84 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>209.5</t>
+          <t>2.09497597679835</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>203.25</t>
+          <t>2.03254429287375</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>198.57</t>
+          <t>1.98571969254371</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>200.68</t>
+          <t>2.00680246205989</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>214.78</t>
+          <t>2.14778359601595</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>201.6</t>
+          <t>2.01596978653251</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>187.97</t>
+          <t>1.87968598430778</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>187.73</t>
+          <t>1.87733570944902</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>191.95</t>
+          <t>1.91950375467603</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>179.47</t>
+          <t>1.79474494207034</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>182.31</t>
+          <t>1.82312781930401</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>176.5</t>
+          <t>1.76498214335131</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>170.13</t>
+          <t>1.7012999715635</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>163.31</t>
+          <t>1.63308653895073</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>157.88</t>
+          <t>1.57875536457891</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2423,84 +2428,84 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>281.85</t>
+          <t>2.81846259490818</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>267.67</t>
+          <t>2.67674718883161</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>256.86</t>
+          <t>2.56863595379951</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>250.72</t>
+          <t>2.50721577687853</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>259.05</t>
+          <t>2.59051031441751</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>250.26</t>
+          <t>2.50255516161597</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>240.73</t>
+          <t>2.40734917201809</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>249.04</t>
+          <t>2.49044185043385</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>259.27</t>
+          <t>2.5927382666</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>253.68</t>
+          <t>2.53679423694674</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>246.09</t>
+          <t>2.46089440017955</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>222.48</t>
+          <t>2.22480755108544</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>222.36</t>
+          <t>2.22362255895874</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>225.43</t>
+          <t>2.25433939057436</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>222.19</t>
+          <t>2.22194633687185</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2510,84 +2515,84 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>199.99</t>
+          <t>1.99990489404837</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>187.14</t>
+          <t>1.87144391628585</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>175.38</t>
+          <t>1.75383324002244</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>169.67</t>
+          <t>1.69673269956952</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>180.85</t>
+          <t>1.80849162286886</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>167.41</t>
+          <t>1.67412325748656</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>176.18</t>
+          <t>1.76182176849583</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>188.21</t>
+          <t>1.88206696773938</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>219.49</t>
+          <t>2.19487238611565</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>200.91</t>
+          <t>2.00908579848113</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>215.65</t>
+          <t>2.1564612150887</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>217.97</t>
+          <t>2.17969955722284</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>223.51</t>
+          <t>2.23510193857719</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>221.22</t>
+          <t>2.21222153673473</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>213.47</t>
+          <t>2.13470148178362</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2597,84 +2602,84 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>239.95</t>
+          <t>2.39949075348055</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>230.74</t>
+          <t>2.30742362195402</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>226.65</t>
+          <t>2.26651804482379</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>225.51</t>
+          <t>2.25507787084651</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>240.02</t>
+          <t>2.40021647657668</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>235.46</t>
+          <t>2.3545787398763</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>226.21</t>
+          <t>2.26210913973174</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>228.36</t>
+          <t>2.28358262618446</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>242.87</t>
+          <t>2.42865728311895</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>233.29</t>
+          <t>2.33289769916054</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>236.01</t>
+          <t>2.36013198961979</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>229.12</t>
+          <t>2.29121456365263</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>221.55</t>
+          <t>2.21551638017927</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>213.21</t>
+          <t>2.13205620776084</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>206.81</t>
+          <t>2.06812674110742</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Coreia do Sul</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2684,84 +2689,84 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>264.2</t>
+          <t>2.64203673908373</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>252.17</t>
+          <t>2.52169525034348</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>249.89</t>
+          <t>2.49893069174484</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>251.14</t>
+          <t>2.51144980478821</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>264.75</t>
+          <t>2.64749110820945</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>259.27</t>
+          <t>2.59274472219153</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>245.57</t>
+          <t>2.4557305886614</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>252.04</t>
+          <t>2.52037043052123</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>262.97</t>
+          <t>2.62966235479577</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>253.04</t>
+          <t>2.53043799191937</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>253.6</t>
+          <t>2.53603429180441</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>246.71</t>
+          <t>2.46713774429211</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>239.09</t>
+          <t>2.39088931088908</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>230.47</t>
+          <t>2.30472065255997</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>223.91</t>
+          <t>2.23910923298113</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lituânia</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2771,84 +2776,84 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>223.99</t>
+          <t>2.23994036448918</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>215.81</t>
+          <t>2.15812266653536</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>206.26</t>
+          <t>2.06264139025435</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>204.27</t>
+          <t>2.0427292409708</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>214.16</t>
+          <t>2.14162668779394</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>208.92</t>
+          <t>2.08923773172362</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>201.33</t>
+          <t>2.01329459181586</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>208.34</t>
+          <t>2.08335209752654</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>236.64</t>
+          <t>2.36641905857022</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>212.43</t>
+          <t>2.12428114279597</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>217.29</t>
+          <t>2.1729443297913</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>214.2</t>
+          <t>2.14199457994761</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>218.85</t>
+          <t>2.18845127829858</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>212.7</t>
+          <t>2.1269952210444</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>209.35</t>
+          <t>2.09349834677737</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luxemburgo</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2858,84 +2863,84 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>318.93</t>
+          <t>3.18933366032101</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>308.39</t>
+          <t>3.08385401550368</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>299.81</t>
+          <t>2.99810113846762</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>267.86</t>
+          <t>2.67858210884494</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>254.86</t>
+          <t>2.54861001545776</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>222.45</t>
+          <t>2.22450563212408</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>212.26</t>
+          <t>2.122649889677</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>216.39</t>
+          <t>2.16390838595466</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>262.93</t>
+          <t>2.62932254354211</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>227.17</t>
+          <t>2.27174767652337</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>234.88</t>
+          <t>2.34876812248288</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>222.92</t>
+          <t>2.2291955780604</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>220.36</t>
+          <t>2.20364142905195</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>211.26</t>
+          <t>2.1126235312356</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>205.95</t>
+          <t>2.05948291318002</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Letônia</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2945,84 +2950,84 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>204.38</t>
+          <t>2.04380310418494</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>193.98</t>
+          <t>1.93977292043054</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>185.37</t>
+          <t>1.85374015298091</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>183.13</t>
+          <t>1.83128086251183</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>193.35</t>
+          <t>1.93346617116337</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>189.94</t>
+          <t>1.89941135367234</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>183.17</t>
+          <t>1.83169748716191</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>191.04</t>
+          <t>1.91036372688989</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>222.01</t>
+          <t>2.22009535294332</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>197.18</t>
+          <t>1.97183448272827</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>198.73</t>
+          <t>1.98733223977999</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>189.85</t>
+          <t>1.89851911791254</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>186.35</t>
+          <t>1.86345158277339</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>170.14</t>
+          <t>1.70139550915943</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>171.79</t>
+          <t>1.71785133071052</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3032,84 +3037,84 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>183.19</t>
+          <t>1.83185308011029</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>179.61</t>
+          <t>1.79609337785052</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>172.89</t>
+          <t>1.72887052660705</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>167.58</t>
+          <t>1.67583788041072</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>177.1</t>
+          <t>1.77101657501061</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>171.16</t>
+          <t>1.71163879944212</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>167.89</t>
+          <t>1.67893962545166</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>174.08</t>
+          <t>1.74077591980319</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>180.54</t>
+          <t>1.80540694870462</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>174.81</t>
+          <t>1.7480858410423</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>190.35</t>
+          <t>1.90354159650344</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>178.55</t>
+          <t>1.78552777588891</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>173.59</t>
+          <t>1.73585179458663</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>169.7</t>
+          <t>1.69700835780261</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>164.04</t>
+          <t>1.64042920567438</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3119,84 +3124,84 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>163.68</t>
+          <t>1.63678837524516</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>157.78</t>
+          <t>1.57775612314792</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>149.32</t>
+          <t>1.49322303977444</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>145.77</t>
+          <t>1.45770182380635</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>154.68</t>
+          <t>1.54682715504669</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>150.57</t>
+          <t>1.50569040569659</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>143.78</t>
+          <t>1.43783396699781</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>147.34</t>
+          <t>1.47340075946385</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>227.52</t>
+          <t>2.27524575211545</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>160.25</t>
+          <t>1.60245689500991</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>160.85</t>
+          <t>1.60848525847223</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>157.96</t>
+          <t>1.57955577567188</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>157.28</t>
+          <t>1.57281301179332</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>152.64</t>
+          <t>1.52635201670177</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>150.12</t>
+          <t>1.50119910903309</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Países Baixos</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3206,84 +3211,84 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>254.47</t>
+          <t>2.5446621291707</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>246.93</t>
+          <t>2.46934980792738</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>235.32</t>
+          <t>2.35322513253852</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>231.8</t>
+          <t>2.31798961661069</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>244.82</t>
+          <t>2.44822630415783</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>229.16</t>
+          <t>2.29161838665584</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>217.95</t>
+          <t>2.17951985499898</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>221.59</t>
+          <t>2.21590073992427</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>257.22</t>
+          <t>2.57215892013288</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>229.13</t>
+          <t>2.29134168404803</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>231.96</t>
+          <t>2.31963958832513</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>225.36</t>
+          <t>2.25356531433525</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>230.12</t>
+          <t>2.30115753253666</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>215.83</t>
+          <t>2.15827182259862</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>210.21</t>
+          <t>2.10212371898151</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3293,84 +3298,84 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>203.03</t>
+          <t>2.03030157377649</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>193.03</t>
+          <t>1.93028328564004</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>184.49</t>
+          <t>1.8449030975248</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>181.66</t>
+          <t>1.81662949709829</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>191.26</t>
+          <t>1.9126472237251</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>185.7</t>
+          <t>1.85696627450787</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>180.7</t>
+          <t>1.80696401820505</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>182.11</t>
+          <t>1.82107078950656</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>212.57</t>
+          <t>2.12574054646523</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>193.58</t>
+          <t>1.93582172917666</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>202.06</t>
+          <t>2.020591406409</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>198.8</t>
+          <t>1.98799230773746</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>190.1</t>
+          <t>1.90100391975953</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>189.14</t>
+          <t>1.8913578517268</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>188.17</t>
+          <t>1.88174267697936</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3380,84 +3385,84 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>166.58</t>
+          <t>1.66582453879429</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>158.59</t>
+          <t>1.58594955871647</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>150.28</t>
+          <t>1.50281709146895</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>147.44</t>
+          <t>1.47442189937537</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>155.36</t>
+          <t>1.55360372861761</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>150.87</t>
+          <t>1.50868798021721</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>142.79</t>
+          <t>1.42790472833294</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>147.14</t>
+          <t>1.47143109001522</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>227.5</t>
+          <t>2.27504254827536</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>161.56</t>
+          <t>1.61558782214531</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>163.26</t>
+          <t>1.63256964180266</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>159.4</t>
+          <t>1.59399992140131</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>158.12</t>
+          <t>1.58116190241498</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>157.72</t>
+          <t>1.57722211240466</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>155.86</t>
+          <t>1.55864645202877</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3467,84 +3472,84 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>140.49</t>
+          <t>1.40488311142638</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>132.44</t>
+          <t>1.32440043877279</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>129.88</t>
+          <t>1.29877323234051</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>123.95</t>
+          <t>1.23948140407321</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>142.66</t>
+          <t>1.42655553301487</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>138.77</t>
+          <t>1.38767269699938</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>125.17</t>
+          <t>1.25168122603708</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>129.65</t>
+          <t>1.29651818200863</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>218.68</t>
+          <t>2.18677437330611</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>145.18</t>
+          <t>1.45177848232711</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>146.52</t>
+          <t>1.46519768912165</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>147.86</t>
+          <t>1.47862151288141</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>147.94</t>
+          <t>1.47935456840692</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>145.85</t>
+          <t>1.45850784560102</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>147.25</t>
+          <t>1.47245451961797</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rússia</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3554,84 +3559,84 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>137.2</t>
+          <t>1.372005705562</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>124.99</t>
+          <t>1.24994849380652</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>125.6</t>
+          <t>1.25603096320692</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>124.81</t>
+          <t>1.24807532719216</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>125.21</t>
+          <t>1.25211181444956</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>124.03</t>
+          <t>1.24029641429762</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>121.85</t>
+          <t>1.2184937467242</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>129.48</t>
+          <t>1.29480126040942</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>138.05</t>
+          <t>1.38048746766743</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>131.24</t>
+          <t>1.31239950404768</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>133.95</t>
+          <t>1.33954517394971</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>129.35</t>
+          <t>1.29351790378151</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>123.28</t>
+          <t>1.2328474724888</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>117.73</t>
+          <t>1.17728611637662</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>116.87</t>
+          <t>1.16865132103991</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3641,84 +3646,84 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>196.72</t>
+          <t>1.96718949230029</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>186.88</t>
+          <t>1.86880095787918</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>178.78</t>
+          <t>1.78783218770531</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>177.11</t>
+          <t>1.77107811962931</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>175.53</t>
+          <t>1.75527491892645</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>165.62</t>
+          <t>1.65621995124424</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>164.37</t>
+          <t>1.64365209403404</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>184.92</t>
+          <t>1.84924434740061</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>217.35</t>
+          <t>2.17352302301362</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>181.89</t>
+          <t>1.81888865891484</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>180.15</t>
+          <t>1.80145501502784</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>171.46</t>
+          <t>1.71458416361133</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>174.81</t>
+          <t>1.74813880317204</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>170.51</t>
+          <t>1.70505446005293</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>171.43</t>
+          <t>1.71426138337683</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3728,84 +3733,84 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>185.81</t>
+          <t>1.85808323376178</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>178.32</t>
+          <t>1.78321740842958</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>172.29</t>
+          <t>1.72289563699208</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>171.11</t>
+          <t>1.71114332636595</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>185.81</t>
+          <t>1.85807579782732</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>174.53</t>
+          <t>1.74526736069736</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>164.53</t>
+          <t>1.64534876870346</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>168.32</t>
+          <t>1.68324075472764</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>184.41</t>
+          <t>1.84411347660231</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>176.49</t>
+          <t>1.76489826928063</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>180.91</t>
+          <t>1.80914983082193</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>187.61</t>
+          <t>1.87607677513694</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>183.82</t>
+          <t>1.83819309742267</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>178.58</t>
+          <t>1.78581119228827</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>174.72</t>
+          <t>1.74717743820562</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3815,84 +3820,84 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>243.41</t>
+          <t>2.43406959053595</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>234.45</t>
+          <t>2.34451858096284</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>227.49</t>
+          <t>2.27493198584509</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>226.33</t>
+          <t>2.26325010820376</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>237.38</t>
+          <t>2.37383719431583</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>242.4</t>
+          <t>2.42403707309353</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>238.24</t>
+          <t>2.38237625405235</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>240.1</t>
+          <t>2.40100892573164</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>265.82</t>
+          <t>2.65824507018357</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>246.45</t>
+          <t>2.46454854051147</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>252.2</t>
+          <t>2.5220434454994</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>249.08</t>
+          <t>2.49079205015269</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>245.3</t>
+          <t>2.45301372748389</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>232.61</t>
+          <t>2.32611227056592</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>225.22</t>
+          <t>2.25216012110131</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3902,84 +3907,84 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>136.56</t>
+          <t>1.36560903190815</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>131.9</t>
+          <t>1.31897906614767</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>130.07</t>
+          <t>1.30071780826927</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>129.62</t>
+          <t>1.29621568364929</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>141.22</t>
+          <t>1.41216989646994</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>138.54</t>
+          <t>1.38539430011869</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>133.16</t>
+          <t>1.33159297159862</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>136.83</t>
+          <t>1.36833851556321</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>148.09</t>
+          <t>1.48093518557588</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>137.27</t>
+          <t>1.3727217951801</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>144.23</t>
+          <t>1.44227238172727</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>143.85</t>
+          <t>1.43846945261545</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>143.73</t>
+          <t>1.43734204738779</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>141.02</t>
+          <t>1.4102193149497</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>141.9</t>
+          <t>1.41904016222537</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>China: Taiwan</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3989,84 +3994,84 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>256.99</t>
+          <t>2.56992851657961</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>248.51</t>
+          <t>2.48509311358276</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>242.1</t>
+          <t>2.42097408141616</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>242.36</t>
+          <t>2.42357868170588</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>255.89</t>
+          <t>2.55893298095507</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>251.87</t>
+          <t>2.51873778421087</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>245.77</t>
+          <t>2.45765164044549</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>253.69</t>
+          <t>2.5368735984762</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>264.33</t>
+          <t>2.64334487511632</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>253.93</t>
+          <t>2.53933401175424</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>262.32</t>
+          <t>2.6232131803349</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>257.23</t>
+          <t>2.57228542062822</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>252.06</t>
+          <t>2.52059071544297</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>245.06</t>
+          <t>2.45057561832259</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>235.72</t>
+          <t>2.35718806314229</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4076,84 +4081,84 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>219.13</t>
+          <t>2.19129607375313</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>211.26</t>
+          <t>2.11261929922387</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>200.22</t>
+          <t>2.00223926162103</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>197.08</t>
+          <t>1.97081638746766</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>209.33</t>
+          <t>2.09330360654566</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>196.29</t>
+          <t>1.96288513305133</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>188.08</t>
+          <t>1.8808275072252</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>192.3</t>
+          <t>1.9229618792991</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>202.87</t>
+          <t>2.02872828917043</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>192.14</t>
+          <t>1.92142968114887</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>195.56</t>
+          <t>1.95557135858642</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>188.1</t>
+          <t>1.8810214104571</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>188.78</t>
+          <t>1.88775024539647</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>181.21</t>
+          <t>1.81208526249068</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>178.66</t>
+          <t>1.78656608151661</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Resto do mundo</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4163,84 +4168,84 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>219.05</t>
+          <t>2.19049719192514</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>210.37</t>
+          <t>2.10370921406971</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>203.14</t>
+          <t>2.03141108032851</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>201.78</t>
+          <t>2.01782559790231</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>212.5</t>
+          <t>2.12504178930266</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>202.91</t>
+          <t>2.02912786579775</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>196.15</t>
+          <t>1.96151944566172</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>2.02999091863113</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>227.02</t>
+          <t>2.27016540773809</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>206.81</t>
+          <t>2.0680500698185</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>209.28</t>
+          <t>2.09284450520906</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>203.45</t>
+          <t>2.03451754236666</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>198.85</t>
+          <t>1.98847752331369</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>1.9199923946533</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>189.83</t>
+          <t>1.89830444190864</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mundo</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4250,84 +4255,84 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>221.69</t>
+          <t>2.21688051812419</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>211.97</t>
+          <t>2.11967467211267</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>204.32</t>
+          <t>2.04315044571125</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>202.28</t>
+          <t>2.02284825303909</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>216.2</t>
+          <t>2.16201602811269</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>206.89</t>
+          <t>2.06892646383661</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>199.02</t>
+          <t>1.99022958520788</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>204.04</t>
+          <t>2.04037021260873</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>220.11</t>
+          <t>2.20113984676448</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>207.16</t>
+          <t>2.07158115360121</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>210.03</t>
+          <t>2.10033424560233</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>202.74</t>
+          <t>2.02742225865349</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>199.02</t>
+          <t>1.99016344180161</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>191.35</t>
+          <t>1.91349055275255</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>187.78</t>
+          <t>1.87783399760359</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4339,7 +4344,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4351,7 +4356,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4363,7 +4368,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Africa do Sul</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4375,7 +4380,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Resto do mundo - Asia</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4387,7 +4392,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Resto do mundo - America</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4399,7 +4404,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Resto do mundo - Europa</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4411,7 +4416,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Resto do mundo - Africa</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4423,7 +4428,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Resto do mundo - Oriente Medio</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4470,6 +4475,11 @@
           <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4504,6 +4514,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Ochoa 1</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpO1</t>
